--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260610.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.24%</t>
+          <t>11.94%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.20%</t>
+          <t>10.25%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>8.97%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.38%</t>
+          <t>7.18%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.55%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>3.82%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.76%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.29%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NXT US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>NEXTracker公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>73,056</t>
+          <t>33,008</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>NXT US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>NEXTracker公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>33,008</t>
+          <t>73,056</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>SWX US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>西南天然氣控股公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,103</t>
+          <t>65,675</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SWX US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>西南天然氣控股公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>65,675</t>
+          <t>21,103</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1100,73 +1100,73 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>14,428</t>
+          <t>53,140</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>53,140</t>
+          <t>129,716</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>129,716</t>
+          <t>31,595</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>31,595</t>
+          <t>14,428</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1320,24 +1320,24 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>202606ESM6</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>15,450</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>202606ESM6</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15,450</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1540,68 +1540,68 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>29,949</t>
+          <t>77,540</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>77,540</t>
+          <t>29,949</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>8,750</t>
+          <t>75,391</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>75,391</t>
+          <t>8,750</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.02%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>163,041,692</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
